--- a/data/research_summary.xlsx
+++ b/data/research_summary.xlsx
@@ -24,11 +24,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -39,44 +38,47 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Noto Sans SC"/>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="001B2A4A"/>
       <sz val="16"/>
     </font>
     <font>
-      <name val="Noto Sans SC"/>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Noto Sans SC"/>
+      <name val="Calibri"/>
       <color rgb="0037352F"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Noto Sans SC"/>
+      <name val="Calibri"/>
       <color rgb="008C8A84"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Noto Sans SC"/>
+      <name val="Calibri"/>
       <color rgb="001B7D46"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Noto Sans SC"/>
+      <name val="Calibri"/>
       <color rgb="00D4820A"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Noto Sans SC"/>
+      <name val="Calibri"/>
       <color rgb="00C0392B"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Noto Sans SC"/>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="001B2A4A"/>
-      <sz val="11"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="9">
@@ -157,7 +159,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -166,7 +168,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -187,16 +189,16 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="9" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="9" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -566,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="B2:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -595,7 +597,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="38" customHeight="1">
+    <row r="5" ht="22" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Project type</t>
@@ -627,11 +629,11 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>heyjdy (GitHub) — Research &amp; Data Support</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="54" customHeight="1">
+          <t>Research &amp; Data Support — Concept Portfolio</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
       <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Fictional-data disclaimer</t>
@@ -655,7 +657,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="38" customHeight="1">
+    <row r="10" ht="22" customHeight="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Raw Data sheet</t>
@@ -703,7 +705,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="54" customHeight="1">
+    <row r="14" ht="22" customHeight="1">
       <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Confidence levels</t>
@@ -727,7 +729,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="38" customHeight="1">
+    <row r="16" ht="22" customHeight="1">
       <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Normalization conventions</t>
@@ -740,7 +742,7 @@
       </c>
     </row>
     <row r="17" ht="22" customHeight="1"/>
-    <row r="18" ht="70" customHeight="1">
+    <row r="18" ht="22" customHeight="1">
       <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Questions about this demo workbook: see README.md in the project folder.</t>
@@ -762,16 +764,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S26"/>
+  <dimension ref="B2:S26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
@@ -781,9 +783,9 @@
     <col width="30" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="27" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
+    <col width="29" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1"/>
@@ -795,7 +797,7 @@
       </c>
     </row>
     <row r="3" ht="8" customHeight="1"/>
-    <row r="4" ht="70" customHeight="1">
+    <row r="4" ht="28" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Company / Product</t>
@@ -887,7 +889,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="54" customHeight="1">
+    <row r="5" ht="22" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>TaskPilot Pro</t>
@@ -975,7 +977,7 @@
         <v>46249</v>
       </c>
     </row>
-    <row r="6" ht="54" customHeight="1">
+    <row r="6" ht="22" customHeight="1">
       <c r="B6" s="4" t="inlineStr">
         <is>
           <t>NoteNest</t>
@@ -1063,7 +1065,7 @@
         <v>46238</v>
       </c>
     </row>
-    <row r="7" ht="38" customHeight="1">
+    <row r="7" ht="22" customHeight="1">
       <c r="B7" s="3" t="inlineStr">
         <is>
           <t>FlowDesk</t>
@@ -1151,7 +1153,7 @@
         <v>46231</v>
       </c>
     </row>
-    <row r="8" ht="38" customHeight="1">
+    <row r="8" ht="22" customHeight="1">
       <c r="B8" s="4" t="inlineStr">
         <is>
           <t>MindMesh</t>
@@ -1239,7 +1241,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="9" ht="38" customHeight="1">
+    <row r="9" ht="22" customHeight="1">
       <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Scheduly</t>
@@ -1323,7 +1325,7 @@
         <v>46203</v>
       </c>
     </row>
-    <row r="10" ht="54" customHeight="1">
+    <row r="10" ht="22" customHeight="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
           <t>DocuFlow</t>
@@ -1411,7 +1413,7 @@
         <v>46225</v>
       </c>
     </row>
-    <row r="11" ht="38" customHeight="1">
+    <row r="11" ht="22" customHeight="1">
       <c r="B11" s="3" t="inlineStr">
         <is>
           <t>TeamSync</t>
@@ -1495,7 +1497,7 @@
         <v>46161</v>
       </c>
     </row>
-    <row r="12" ht="38" customHeight="1">
+    <row r="12" ht="22" customHeight="1">
       <c r="B12" s="4" t="inlineStr">
         <is>
           <t>FocusForge</t>
@@ -1583,7 +1585,7 @@
         <v>46236</v>
       </c>
     </row>
-    <row r="13" ht="38" customHeight="1">
+    <row r="13" ht="22" customHeight="1">
       <c r="B13" s="3" t="inlineStr">
         <is>
           <t>InBoxZero</t>
@@ -1667,7 +1669,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="14" ht="38" customHeight="1">
+    <row r="14" ht="22" customHeight="1">
       <c r="B14" s="4" t="inlineStr">
         <is>
           <t>MeetMate</t>
@@ -1751,7 +1753,7 @@
         <v>46255</v>
       </c>
     </row>
-    <row r="15" ht="38" customHeight="1">
+    <row r="15" ht="22" customHeight="1">
       <c r="B15" s="3" t="inlineStr">
         <is>
           <t>PlanCraft</t>
@@ -1835,7 +1837,7 @@
         <v>46214</v>
       </c>
     </row>
-    <row r="16" ht="38" customHeight="1">
+    <row r="16" ht="22" customHeight="1">
       <c r="B16" s="4" t="inlineStr">
         <is>
           <t>WriteWise</t>
@@ -1919,7 +1921,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="17" ht="54" customHeight="1">
+    <row r="17" ht="22" customHeight="1">
       <c r="B17" s="3" t="inlineStr">
         <is>
           <t>ChronoBase</t>
@@ -2007,7 +2009,7 @@
         <v>46178</v>
       </c>
     </row>
-    <row r="18" ht="38" customHeight="1">
+    <row r="18" ht="22" customHeight="1">
       <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Kanbanly</t>
@@ -2091,7 +2093,7 @@
         <v>46264</v>
       </c>
     </row>
-    <row r="19" ht="38" customHeight="1">
+    <row r="19" ht="22" customHeight="1">
       <c r="B19" s="3" t="inlineStr">
         <is>
           <t>SummarEase</t>
@@ -2179,7 +2181,7 @@
         <v>46274</v>
       </c>
     </row>
-    <row r="20" ht="70" customHeight="1">
+    <row r="20" ht="22" customHeight="1">
       <c r="B20" s="4" t="inlineStr">
         <is>
           <t>WorkWhale</t>
@@ -2267,7 +2269,7 @@
         <v>46285</v>
       </c>
     </row>
-    <row r="21" ht="38" customHeight="1">
+    <row r="21" ht="22" customHeight="1">
       <c r="B21" s="3" t="inlineStr">
         <is>
           <t>GoalGrid</t>
@@ -2355,7 +2357,7 @@
         <v>46222</v>
       </c>
     </row>
-    <row r="22" ht="54" customHeight="1">
+    <row r="22" ht="22" customHeight="1">
       <c r="B22" s="4" t="inlineStr">
         <is>
           <t>AutoMateHQ</t>
@@ -2439,7 +2441,7 @@
         <v>46261</v>
       </c>
     </row>
-    <row r="23" ht="38" customHeight="1">
+    <row r="23" ht="22" customHeight="1">
       <c r="B23" s="3" t="inlineStr">
         <is>
           <t>ClientDesk</t>
@@ -2523,7 +2525,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="24" ht="38" customHeight="1">
+    <row r="24" ht="22" customHeight="1">
       <c r="B24" s="4" t="inlineStr">
         <is>
           <t>SprintBoard</t>
@@ -2608,7 +2610,7 @@
       </c>
     </row>
     <row r="25" ht="22" customHeight="1"/>
-    <row r="26" ht="86" customHeight="1">
+    <row r="26" ht="22" customHeight="1">
       <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Concept Project — all companies, prices, and sources are fictional demo data. Confidence: High / Medium / Needs verification.</t>
@@ -2631,14 +2633,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R28"/>
+  <dimension ref="B2:R28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
@@ -2650,8 +2652,8 @@
     <col width="28" customWidth="1" min="14" max="14"/>
     <col width="28" customWidth="1" min="15" max="15"/>
     <col width="28" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="28" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1"/>
@@ -2750,7 +2752,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="86" customHeight="1">
+    <row r="5" ht="22" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>R01</t>
@@ -2837,7 +2839,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="86" customHeight="1">
+    <row r="6" ht="22" customHeight="1">
       <c r="B6" s="4" t="inlineStr">
         <is>
           <t>R02</t>
@@ -2920,7 +2922,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
+    <row r="7" ht="22" customHeight="1">
       <c r="B7" s="3" t="inlineStr">
         <is>
           <t>R03</t>
@@ -3007,7 +3009,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="54" customHeight="1">
+    <row r="8" ht="22" customHeight="1">
       <c r="B8" s="4" t="inlineStr">
         <is>
           <t>R04</t>
@@ -3094,7 +3096,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="54" customHeight="1">
+    <row r="9" ht="22" customHeight="1">
       <c r="B9" s="3" t="inlineStr">
         <is>
           <t>R05</t>
@@ -3173,7 +3175,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="54" customHeight="1">
+    <row r="10" ht="22" customHeight="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
           <t>R06</t>
@@ -3260,7 +3262,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="38" customHeight="1">
+    <row r="11" ht="22" customHeight="1">
       <c r="B11" s="3" t="inlineStr">
         <is>
           <t>R07</t>
@@ -3343,7 +3345,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="38" customHeight="1">
+    <row r="12" ht="22" customHeight="1">
       <c r="B12" s="4" t="inlineStr">
         <is>
           <t>R08</t>
@@ -3430,7 +3432,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="38" customHeight="1">
+    <row r="13" ht="22" customHeight="1">
       <c r="B13" s="3" t="inlineStr">
         <is>
           <t>R09</t>
@@ -3513,7 +3515,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="38" customHeight="1">
+    <row r="14" ht="22" customHeight="1">
       <c r="B14" s="4" t="inlineStr">
         <is>
           <t>R10</t>
@@ -3596,7 +3598,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="38" customHeight="1">
+    <row r="15" ht="22" customHeight="1">
       <c r="B15" s="3" t="inlineStr">
         <is>
           <t>R11</t>
@@ -3683,7 +3685,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="38" customHeight="1">
+    <row r="16" ht="22" customHeight="1">
       <c r="B16" s="4" t="inlineStr">
         <is>
           <t>R12</t>
@@ -3766,7 +3768,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="38" customHeight="1">
+    <row r="17" ht="22" customHeight="1">
       <c r="B17" s="3" t="inlineStr">
         <is>
           <t>R13</t>
@@ -3853,7 +3855,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="38" customHeight="1">
+    <row r="18" ht="22" customHeight="1">
       <c r="B18" s="4" t="inlineStr">
         <is>
           <t>R14</t>
@@ -3936,7 +3938,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="38" customHeight="1">
+    <row r="19" ht="22" customHeight="1">
       <c r="B19" s="3" t="inlineStr">
         <is>
           <t>R15</t>
@@ -4019,7 +4021,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="54" customHeight="1">
+    <row r="20" ht="22" customHeight="1">
       <c r="B20" s="4" t="inlineStr">
         <is>
           <t>R16</t>
@@ -4106,7 +4108,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="38" customHeight="1">
+    <row r="21" ht="22" customHeight="1">
       <c r="B21" s="3" t="inlineStr">
         <is>
           <t>R17</t>
@@ -4193,7 +4195,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="54" customHeight="1">
+    <row r="22" ht="22" customHeight="1">
       <c r="B22" s="4" t="inlineStr">
         <is>
           <t>R18</t>
@@ -4276,7 +4278,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="38" customHeight="1">
+    <row r="23" ht="22" customHeight="1">
       <c r="B23" s="3" t="inlineStr">
         <is>
           <t>R19</t>
@@ -4359,7 +4361,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="38" customHeight="1">
+    <row r="24" ht="22" customHeight="1">
       <c r="B24" s="4" t="inlineStr">
         <is>
           <t>R20</t>
@@ -4442,7 +4444,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="70" customHeight="1">
+    <row r="25" ht="22" customHeight="1">
       <c r="B25" s="3" t="inlineStr">
         <is>
           <t>R21</t>
@@ -4517,7 +4519,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="38" customHeight="1">
+    <row r="26" ht="22" customHeight="1">
       <c r="B26" s="4" t="inlineStr">
         <is>
           <t>R22</t>
@@ -4585,7 +4587,7 @@
       </c>
     </row>
     <row r="27" ht="22" customHeight="1"/>
-    <row r="28" ht="118" customHeight="1">
+    <row r="28" ht="22" customHeight="1">
       <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Records R21 and R22 duplicate R01 and R02 under variant names — merged during cleaning. Formatting inconsistencies are intentional (demonstration data).</t>
@@ -4608,16 +4610,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="B2:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
     <col width="48" customWidth="1" min="5" max="5"/>
     <col width="48" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1"/>
@@ -4661,7 +4663,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
+    <row r="5" ht="22" customHeight="1">
       <c r="B5" s="13" t="n">
         <v>1</v>
       </c>
@@ -4693,7 +4695,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="54" customHeight="1">
+    <row r="6" ht="22" customHeight="1">
       <c r="B6" s="14" t="n">
         <v>2</v>
       </c>
@@ -4724,7 +4726,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="54" customHeight="1">
+    <row r="7" ht="22" customHeight="1">
       <c r="B7" s="13" t="n">
         <v>3</v>
       </c>
@@ -4755,7 +4757,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="38" customHeight="1">
+    <row r="8" ht="22" customHeight="1">
       <c r="B8" s="14" t="n">
         <v>4</v>
       </c>
@@ -4785,7 +4787,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
+    <row r="9" ht="22" customHeight="1">
       <c r="B9" s="13" t="n">
         <v>5</v>
       </c>
@@ -4816,7 +4818,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="54" customHeight="1">
+    <row r="10" ht="22" customHeight="1">
       <c r="B10" s="14" t="n">
         <v>6</v>
       </c>
@@ -4847,7 +4849,7 @@
       </c>
     </row>
     <row r="11" ht="22" customHeight="1"/>
-    <row r="12" ht="294" customHeight="1">
+    <row r="12" ht="22" customHeight="1">
       <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Every transformation in this log is reproducible: raw record IDs reference the Raw Data sheet.</t>
@@ -4869,12 +4871,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="B2:D64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -5003,14 +5005,14 @@
       </c>
     </row>
     <row r="14" ht="22" customHeight="1"/>
-    <row r="15" ht="26" customHeight="1">
+    <row r="15" ht="22" customHeight="1">
       <c r="B15" s="15" t="inlineStr">
         <is>
           <t>Products by Category</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1">
+    <row r="16" ht="22" customHeight="1">
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Product category</t>
@@ -5132,14 +5134,14 @@
       </c>
     </row>
     <row r="25" ht="22" customHeight="1"/>
-    <row r="26" ht="26" customHeight="1">
+    <row r="26" ht="22" customHeight="1">
       <c r="B26" s="15" t="inlineStr">
         <is>
           <t>Starting Price Distribution</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="28" customHeight="1">
+    <row r="27" ht="22" customHeight="1">
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Price band (USD/user/mo)</t>
@@ -5209,14 +5211,14 @@
       </c>
     </row>
     <row r="32" ht="22" customHeight="1"/>
-    <row r="33" ht="26" customHeight="1">
+    <row r="33" ht="22" customHeight="1">
       <c r="B33" s="15" t="inlineStr">
         <is>
           <t>Price Statistics</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="28" customHeight="1">
+    <row r="34" ht="22" customHeight="1">
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Statistic</t>
@@ -5277,14 +5279,14 @@
       </c>
     </row>
     <row r="39" ht="22" customHeight="1"/>
-    <row r="40" ht="26" customHeight="1">
+    <row r="40" ht="22" customHeight="1">
       <c r="B40" s="15" t="inlineStr">
         <is>
           <t>Free Plan Availability</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="28" customHeight="1">
+    <row r="41" ht="22" customHeight="1">
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Availability</t>
@@ -5341,14 +5343,14 @@
       </c>
     </row>
     <row r="45" ht="22" customHeight="1"/>
-    <row r="46" ht="26" customHeight="1">
+    <row r="46" ht="22" customHeight="1">
       <c r="B46" s="15" t="inlineStr">
         <is>
           <t>AI Feature Adoption</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="28" customHeight="1">
+    <row r="47" ht="22" customHeight="1">
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>AI features</t>
@@ -5392,14 +5394,14 @@
       </c>
     </row>
     <row r="50" ht="22" customHeight="1"/>
-    <row r="51" ht="26" customHeight="1">
+    <row r="51" ht="22" customHeight="1">
       <c r="B51" s="15" t="inlineStr">
         <is>
           <t>Target Customer Distribution</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="28" customHeight="1">
+    <row r="52" ht="22" customHeight="1">
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>Target customer</t>
@@ -5469,14 +5471,14 @@
       </c>
     </row>
     <row r="57" ht="22" customHeight="1"/>
-    <row r="58" ht="26" customHeight="1">
+    <row r="58" ht="22" customHeight="1">
       <c r="B58" s="15" t="inlineStr">
         <is>
           <t>Data Confidence</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="28" customHeight="1">
+    <row r="59" ht="22" customHeight="1">
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Confidence level</t>
@@ -5533,7 +5535,7 @@
       </c>
     </row>
     <row r="63" ht="22" customHeight="1"/>
-    <row r="64" ht="54" customHeight="1">
+    <row r="64" ht="22" customHeight="1">
       <c r="B64" s="5" t="inlineStr">
         <is>
           <t>All figures derived from the Clean Data sheet. Concept Project — fictional demo data.</t>
@@ -5563,12 +5565,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="B2:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="47" customWidth="1" min="3" max="3"/>
     <col width="52" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -5604,7 +5606,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="38" customHeight="1">
+    <row r="5" ht="22" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Source recorded</t>
@@ -5626,7 +5628,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="54" customHeight="1">
+    <row r="6" ht="22" customHeight="1">
       <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Duplicate checked</t>
@@ -5648,7 +5650,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="54" customHeight="1">
+    <row r="7" ht="22" customHeight="1">
       <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Pricing normalized</t>
@@ -5670,7 +5672,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="38" customHeight="1">
+    <row r="8" ht="22" customHeight="1">
       <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Missing values flagged</t>
@@ -5692,7 +5694,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="54" customHeight="1">
+    <row r="9" ht="22" customHeight="1">
       <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Unclear claims marked for verification</t>
@@ -5714,7 +5716,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="38" customHeight="1">
+    <row r="10" ht="22" customHeight="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
           <t>No unsupported assumptions</t>
@@ -5736,7 +5738,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="38" customHeight="1">
+    <row r="11" ht="22" customHeight="1">
       <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Dates standardized</t>
@@ -5758,7 +5760,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="38" customHeight="1">
+    <row r="12" ht="22" customHeight="1">
       <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Final manual review completed</t>
@@ -5781,7 +5783,7 @@
       </c>
     </row>
     <row r="13" ht="22" customHeight="1"/>
-    <row r="14" ht="38" customHeight="1">
+    <row r="14" ht="22" customHeight="1">
       <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Quality process mirrors what would be used on a live client engagement.</t>

--- a/data/research_summary.xlsx
+++ b/data/research_summary.xlsx
@@ -713,7 +713,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>High = two sources agree or official info is clear · Medium = single source or a derived value (e.g. annual price / 12) · Needs verification = conflicting or unclear source information.</t>
+          <t>High = official product source with clearly stated values, or two agreeing records · Medium = secondhand source (directory/review) or derived values · Needs verification = conflicting or unclear source information.</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Cross-checked (2 sources) · Single source · Conflicting sources.</t>
+          <t>Cross-checked (2 sources) · Single source · Single source - conflicting details. Source status counts raw records, not trust.</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Currency USD per user per month · dates ISO 8601 (YYYY-MM-DD) · yes/no/trial-only fields · 8 standard product categories.</t>
+          <t>Currency USD per month (per-user where stated) · dates ISO 8601 (YYYY-MM-DD) · yes/no/trial-only fields · 8 standard product categories.</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
@@ -784,7 +784,7 @@
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
     <col width="21" customWidth="1" min="17" max="17"/>
-    <col width="29" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
@@ -830,7 +830,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Starting Price (USD/user/mo)</t>
+          <t>Starting Price (USD/mo)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Yes (up to 3 projects)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
@@ -925,7 +925,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Per user / month (annual discount available)</t>
+          <t>Monthly (annual discount unconfirmed)</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>40+ (Slack Google Workspace Zapier)</t>
+          <t>40+ (Slack, Google, Zapier)</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>Duplicate directory listing (R21) merged during cleaning</t>
+          <t>Duplicate directory listing (R21) merged during cleaning; price matched in both records</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Yes (limited)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H6" s="9" t="n">
@@ -1033,12 +1033,12 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>Web / iOS / Android / Windows / macOS</t>
+          <t>iOS / Android (others not listed)</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>25+ (Google Drive Notion-style embeds)</t>
+          <t>Google Drive and Notion-style embeds (count not stated)</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Per user / month (annual discount available)</t>
+          <t>Per user / month (billed annually)</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Yes - real-time co-editing</t>
+          <t>Yes - real-time collaboration</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>30+ (Slack GitHub Figma)</t>
+          <t>30+ (names not listed)</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>Source price confirmed as annual-billing rate</t>
+          <t>Source note: 'annual price confirmed on pricing page' - price shown is the annual-billing rate; source target: 'small-to-mid teams'</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>Cross-checked (2 sources)</t>
+          <t>Single source</t>
         </is>
       </c>
       <c r="S7" s="8" t="n">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Per user / month</t>
+          <t>Per seat / month</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Yes - live shared boards</t>
+          <t>Yes - live boards</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>12 (Miro-style import)</t>
+          <t>Unknown (source: unsure)</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>Pricing confirmed from a single source only</t>
+          <t>Pricing from a single review-site source only; integrations unknown (source: unsure); source target: 'designers &amp; consultants'</t>
         </is>
       </c>
       <c r="Q8" s="11" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>Web / iOS / Android</t>
+          <t>iOS / Android (web not stated)</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>15 (Google Calendar Outlook Zoom)</t>
+          <t>Google Calendar, Outlook, Zoom (count not stated)</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
@@ -1310,7 +1310,11 @@
           <t>Availability pooling for small teams</t>
         </is>
       </c>
-      <c r="P9" s="3" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>Platforms per source: iOS and Android (web not stated)</t>
+        </is>
+      </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
           <t>High</t>
@@ -1318,7 +1322,7 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>Cross-checked (2 sources)</t>
+          <t>Single source</t>
         </is>
       </c>
       <c r="S9" s="8" t="n">
@@ -1353,7 +1357,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Yes (limited)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H10" s="9" t="n">
@@ -1361,7 +1365,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Per user / month (annual discount available)</t>
+          <t>Per user / month</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1386,7 +1390,7 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>35+ (Google Workspace Slack)</t>
+          <t>35+ (Google Workspace, Slack)</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
@@ -1406,7 +1410,7 @@
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
-          <t>Cross-checked (2 sources)</t>
+          <t>Single source</t>
         </is>
       </c>
       <c r="S10" s="10" t="n">
@@ -1449,7 +1453,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Per user / month (annual discount available)</t>
+          <t>Per user / month</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1474,7 +1478,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>50+ (Slack-compatible app directory)</t>
+          <t>50+ (names not listed)</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -1490,7 +1494,7 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>Cross-checked (2 sources)</t>
+          <t>Single source</t>
         </is>
       </c>
       <c r="S11" s="8" t="n">
@@ -1533,7 +1537,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Per user / month</t>
+          <t>Monthly (per-user basis not stated)</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1558,7 +1562,7 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>8 (Trello Slack)</t>
+          <t>Trello, Slack (count not stated)</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
@@ -1568,7 +1572,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>Price format unclear on source; monthly assumed</t>
+          <t>Price format unclear on source; monthly assumed; per-user basis not stated; directory-listing source</t>
         </is>
       </c>
       <c r="Q12" s="11" t="inlineStr">
@@ -1631,7 +1635,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Yes - shared inboxes with assignment</t>
+          <t>Yes - shared inboxes</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -1646,7 +1650,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>20 (Gmail Outlook Slack)</t>
+          <t>20 (Gmail, Outlook, Slack)</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
@@ -1662,7 +1666,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>Cross-checked (2 sources)</t>
+          <t>Single source</t>
         </is>
       </c>
       <c r="S13" s="8" t="n">
@@ -1705,7 +1709,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Per user / month (annual discount available)</t>
+          <t>Per user / month</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1730,7 +1734,7 @@
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>25 (Zoom Google Meet Slack)</t>
+          <t>Zoom, Google Meet, Slack (count not stated)</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
@@ -1746,7 +1750,7 @@
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
-          <t>Cross-checked (2 sources)</t>
+          <t>Single source</t>
         </is>
       </c>
       <c r="S14" s="10" t="n">
@@ -1789,7 +1793,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Per user / month (annual discount available)</t>
+          <t>Per user / month</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1799,7 +1803,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Yes - plans Gantt and workload views</t>
+          <t>Yes (details not stated)</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -1814,7 +1818,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>45 (Jira import Slack)</t>
+          <t>45 (Jira import, Slack)</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
@@ -1822,7 +1826,11 @@
           <t>AI timeline risk forecasting</t>
         </is>
       </c>
-      <c r="P15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>Source free-plan field says 'trial'; source notes: no free tier, demo on request</t>
+        </is>
+      </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
           <t>High</t>
@@ -1830,7 +1838,7 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>Cross-checked (2 sources)</t>
+          <t>Single source</t>
         </is>
       </c>
       <c r="S15" s="8" t="n">
@@ -1865,7 +1873,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Trial only (7 days)</t>
+          <t>Trial only</t>
         </is>
       </c>
       <c r="H16" s="9" t="n">
@@ -1898,7 +1906,7 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>6 (Google Docs WordPress)</t>
+          <t>Google Docs, WordPress (count not stated)</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
@@ -1914,7 +1922,7 @@
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>Cross-checked (2 sources)</t>
+          <t>Single source</t>
         </is>
       </c>
       <c r="S16" s="10" t="n">
@@ -1949,7 +1957,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Trial only (14 days)</t>
+          <t>Trial only</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
@@ -1967,7 +1975,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Limited - shared timesheets</t>
+          <t>Limited (details not stated)</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -1982,7 +1990,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>14 (QuickBooks FreshBooks)</t>
+          <t>QuickBooks, FreshBooks (count not stated)</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -1992,7 +2000,7 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>Price converted from $108/user/year (annual billing only)</t>
+          <t>Price derived: $108/user/year divided by 12; single source</t>
         </is>
       </c>
       <c r="Q17" s="11" t="inlineStr">
@@ -2037,7 +2045,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>Yes (limited)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H18" s="9" t="n">
@@ -2045,7 +2053,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Per user / month (annual discount available)</t>
+          <t>Per user / month</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -2055,7 +2063,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Yes - boards cards and assignments</t>
+          <t>Yes (details not stated)</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -2070,23 +2078,27 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>18 (Slack Google Drive)</t>
+          <t>Slack, Google Drive (count not stated)</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>Lowest-priced full kanban board in sample</t>
-        </is>
-      </c>
-      <c r="P18" s="4" t="inlineStr"/>
-      <c r="Q18" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Lowest-priced kanban board in the sample (derived from dataset)</t>
+        </is>
+      </c>
+      <c r="P18" s="4" t="inlineStr">
+        <is>
+          <t>Directory-listing source (secondhand)</t>
+        </is>
+      </c>
+      <c r="Q18" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>Cross-checked (2 sources)</t>
+          <t>Single source</t>
         </is>
       </c>
       <c r="S18" s="10" t="n">
@@ -2139,7 +2151,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Limited - shared folders</t>
+          <t>Limited (details not stated)</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -2154,7 +2166,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>5 (Chrome extension Zapier)</t>
+          <t>Chrome extension, Zapier (count not stated)</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -2167,9 +2179,9 @@
           <t>Web-only; no mobile app as of last check</t>
         </is>
       </c>
-      <c r="Q19" s="11" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
@@ -2209,7 +2221,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>Yes (limited)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H20" s="9" t="n">
@@ -2217,7 +2229,7 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Per user / month (annual discount available)</t>
+          <t>Per user / month (conflicting reports)</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -2227,7 +2239,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>Yes - docs tasks and chat</t>
+          <t>Yes (details not stated)</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -2242,12 +2254,12 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>22 (Slack GitHub Notion import)</t>
+          <t>22 (names not listed)</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>Broadest bundled feature set in sample</t>
+          <t>Bundled docs tasks and chat in one workspace</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
@@ -2262,7 +2274,7 @@
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>Conflicting sources</t>
+          <t>Single source - conflicting details</t>
         </is>
       </c>
       <c r="S20" s="10" t="n">
@@ -2305,7 +2317,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Per user / month (annual discount available)</t>
+          <t>Per user / month</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -2315,22 +2327,22 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Yes - OKR check-ins</t>
+          <t>Yes (details not stated)</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>Web / iOS / Android (platform list unclear)</t>
+          <t>Web (others unconfirmed)</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>12 (Slack Jira)</t>
+          <t>Slack, Jira (count not stated)</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -2340,7 +2352,7 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>Mobile platform availability unclear on source</t>
+          <t>Mobile uncertain in source ('yes?'); platforms: web confirmed only</t>
         </is>
       </c>
       <c r="Q21" s="12" t="inlineStr">
@@ -2393,7 +2405,7 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Per user / month (annual discount available)</t>
+          <t>Per user / month</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -2418,12 +2430,12 @@
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>90+ (Slack Gmail Notion HubSpot)</t>
+          <t>90+ (Slack, Gmail, Notion, HubSpot)</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>Deepest automation catalog in sample</t>
+          <t>Largest integration catalog in the sample (derived from dataset)</t>
         </is>
       </c>
       <c r="P22" s="4" t="inlineStr"/>
@@ -2434,7 +2446,7 @@
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>Cross-checked (2 sources)</t>
+          <t>Single source</t>
         </is>
       </c>
       <c r="S22" s="10" t="n">
@@ -2469,7 +2481,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Yes (limited)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
@@ -2477,7 +2489,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Per user / month (annual discount available)</t>
+          <t>Per user / month</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -2502,7 +2514,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>10 (Gmail Stripe)</t>
+          <t>Gmail, Stripe (count not stated)</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
@@ -2518,7 +2530,7 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>Cross-checked (2 sources)</t>
+          <t>Single source</t>
         </is>
       </c>
       <c r="S23" s="8" t="n">
@@ -2561,7 +2573,7 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Per user / month (annual discount available)</t>
+          <t>Per user / month</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2586,7 +2598,7 @@
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>30 (GitHub GitLab Slack)</t>
+          <t>GitHub, GitLab, Slack (count not stated)</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
@@ -2602,7 +2614,7 @@
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>Cross-checked (2 sources)</t>
+          <t>Single source</t>
         </is>
       </c>
       <c r="S24" s="10" t="n">
@@ -4610,7 +4622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G12"/>
+  <dimension ref="B2:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4679,14 +4691,14 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Starting Price: $9.99 / user / month
-Billing Model: Per user / month
-Annual discount: available (unconfirmed)</t>
+          <t>Starting Price: $9.99 / month
+Billing Model: Monthly - annual discount unconfirmed
+Second record (R21): price matched (9.99 USD monthly)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Amount, currency, and billing cycle split into structured fields; unconfirmed terms flagged, confirmed later via the official pricing page.</t>
+          <t>Amount and billing cycle split into structured fields; the second record independently matched the price, while the unconfirmed discount stayed flagged.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -4712,12 +4724,12 @@
       <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Mobile App: Yes
-Platforms: Web, iOS, Android, Windows, macOS</t>
+Platforms: iOS, Android (both records); Web, Windows, macOS (listed once)</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Vague platform wording cross-checked against the second source before being accepted.</t>
+          <t>Vague wording was cross-checked: only iOS and Android are confirmed by both records; the remaining platforms stay single-source listings.</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -4803,8 +4815,9 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Starting Price: $14.00 (official pricing page)
-Directory value flagged as outdated; row marked Needs verification</t>
+          <t>Starting Price: $14.00 (official pricing page figure)
+Directory figure: conflicting - unresolved
+Source status: single record with conflicting details</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -4848,9 +4861,39 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1"/>
-    <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="5" t="inlineStr">
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Integration counts</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>R05 · Scheduly — integrations: "Google Calendar Outlook Zoom"</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Integrations: Google Calendar, Outlook, Zoom (count not stated)</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Named tools are preserved exactly; totals are never invented - rows whose source gives no count say so.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1"/>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Every transformation in this log is reproducible: raw record IDs reference the Raw Data sheet.</t>
         </is>
@@ -4859,7 +4902,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B13:G13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4871,12 +4914,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D64"/>
+  <dimension ref="B2:D70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -4964,7 +5007,7 @@
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>$9.50 / user / mo</t>
+          <t>$9.50 / month</t>
         </is>
       </c>
     </row>
@@ -4976,7 +5019,7 @@
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>$10.16 / user / mo</t>
+          <t>$10.16 / month</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5187,7 @@
     <row r="27" ht="22" customHeight="1">
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Price band (USD/user/mo)</t>
+          <t>Price band (USD/mo)</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -5536,19 +5579,84 @@
     </row>
     <row r="63" ht="22" customHeight="1"/>
     <row r="64" ht="22" customHeight="1">
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>All figures derived from the Clean Data sheet. Concept Project — fictional demo data.</t>
+      <c r="B64" s="15" t="inlineStr">
+        <is>
+          <t>Source Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Source status (raw records)</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Products</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Share</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Single source</t>
+        </is>
+      </c>
+      <c r="C66" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="D66" s="18" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Cross-checked (2 sources)</t>
+        </is>
+      </c>
+      <c r="C67" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D67" s="19" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Single source - conflicting details</t>
+        </is>
+      </c>
+      <c r="C68" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" s="18" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1"/>
+    <row r="70" ht="22" customHeight="1">
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>All figures derived from the Clean Data sheet. Source status counts raw records per product, not trust. Concept Project — fictional demo data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B46:D46"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B70:D70"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B51:D51"/>
     <mergeCell ref="B4:C4"/>
@@ -5570,7 +5678,7 @@
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
     <col width="52" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -5614,12 +5722,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Every fact is traceable to a dated source</t>
+          <t>Each cleaned row maps to a raw record</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>All 22 raw records carry a source type and a last-checked date (ISO 8601).</t>
+          <t>All 20 cleaned rows map to raw records R01-R22, each with a source type and a last-checked date (ISO 8601); derived or uncertain values are documented in Notes.</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -5663,7 +5771,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>All prices converted to USD per user per month; annual-only converted ($108/yr → $9.00/mo) and documented.</t>
+          <t>All prices converted to USD per month (per-user where the source states it); annual-only converted ($108/yr → $9.00/mo) and documented.</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -5729,7 +5837,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>FocusForge monthly-billing assumption and ChronoBase annual conversion are recorded in Notes.</t>
+          <t>A field-by-field traceability audit removed values the sources don't state (platform guesses, integration counts); remaining derivations (FocusForge monthly assumption, ChronoBase conversion) are recorded in Notes.</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -5763,17 +5871,17 @@
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Final manual review completed</t>
+          <t>Final review completed</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>A human pass over the full table</t>
+          <t>Dataset consistency reviewed during project QA</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>All 20 cleaned rows reviewed end-to-end for consistency before delivery.</t>
+          <t>Every cleaned row was re-audited field-by-field against its raw record before publication.</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
